--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484650_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484650_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0114</v>
+        <v>0.2672</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3969</v>
+        <v>0.6032</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3855</v>
+        <v>-0.336</v>
       </c>
       <c r="G2" t="n">
         <v>0.0885</v>
@@ -610,13 +610,13 @@
         <v>0.9163</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.7376</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7526</v>
+        <v>-0.5464</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2407</v>
+        <v>-0.1912</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3224</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5163</v>
+        <v>2.4752</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.8387</v>
+        <v>-2.5414</v>
       </c>
       <c r="G3" t="n">
         <v>-1.7055</v>
@@ -688,13 +688,13 @@
         <v>0.733</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.562</v>
+        <v>-1.3058</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3869</v>
+        <v>-0.428</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1751</v>
+        <v>-0.8778</v>
       </c>
       <c r="V3" t="n">
         <v>2.212</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. CARRION BALLESTER</t>
+          <t>M. GONZALEZ BRU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.3304</v>
+        <v>-1.2386</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6939</v>
+        <v>-0.4389</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.0243</v>
+        <v>-0.7997</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5203</v>
+        <v>-2.3866</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.9895</v>
+        <v>-0.2259</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5099</v>
+        <v>-2.1607</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0944</v>
+        <v>-0.756</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7764</v>
+        <v>0.4427</v>
       </c>
       <c r="L4" t="n">
-        <v>3.318</v>
+        <v>-1.1987</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5741</v>
+        <v>-1.6306</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.7659</v>
+        <v>-0.6686</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1919</v>
+        <v>-0.962</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6675</v>
+        <v>-1.3467</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.5233</v>
+        <v>-0.9498</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1442</v>
+        <v>-0.3969</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6335</v>
+        <v>1.5785</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9554</v>
+        <v>1.267</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5889</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GONZALEZ BRU</t>
+          <t>R. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.4145</v>
+        <v>-1.3614</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5901</v>
+        <v>2.1336</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8245</v>
+        <v>-3.495</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.3866</v>
+        <v>1.5203</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2259</v>
+        <v>-1.9895</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.1607</v>
+        <v>3.5099</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.756</v>
+        <v>4.0944</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4427</v>
+        <v>0.7764</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1987</v>
+        <v>3.318</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6306</v>
+        <v>-2.5741</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6686</v>
+        <v>-2.7659</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.962</v>
+        <v>0.1919</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9163</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5227</v>
+        <v>-1.6985</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.101</v>
+        <v>-1.0837</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4217</v>
+        <v>-0.6149</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5785</v>
+        <v>-0.6335</v>
       </c>
       <c r="W5" t="n">
-        <v>1.267</v>
+        <v>0.9554</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3115</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1923</v>
+        <v>-1.8266</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6308</v>
+        <v>-0.4385</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5615</v>
+        <v>-1.3881</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2996</v>
@@ -922,13 +922,13 @@
         <v>0.5498</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4425</v>
+        <v>-1.0767</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.5784</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6717</v>
+        <v>-0.4983</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.7512</v>
+        <v>-2.5639</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2819</v>
+        <v>-1.2679</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4693</v>
+        <v>-1.2959</v>
       </c>
       <c r="G7" t="n">
         <v>-1.0525</v>
@@ -1000,13 +1000,13 @@
         <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.772</v>
+        <v>-1.5847</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9374</v>
+        <v>-0.9234</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8346</v>
+        <v>-0.6612</v>
       </c>
       <c r="V7" t="n">
         <v>0.6231</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0529</v>
+        <v>-2.9568</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8138</v>
+        <v>-0.7176</v>
       </c>
       <c r="F8" t="n">
         <v>-2.2391</v>
@@ -1078,10 +1078,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6048</v>
+        <v>-0.5087</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2202</v>
+        <v>-0.1241</v>
       </c>
       <c r="U8" t="n">
         <v>-0.3846</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. HORTELANO ESCRIBA</t>
+          <t>S. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.0662</v>
+        <v>-6.3416</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7071</v>
+        <v>-4.2538</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3591</v>
+        <v>-2.0878</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.6606</v>
+        <v>-2.8005</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.7723</v>
+        <v>-2.3099</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.8883</v>
+        <v>-0.4905</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.0653</v>
+        <v>-0.6554</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.2672</v>
+        <v>-1.4154</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.7981</v>
+        <v>0.76</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5953</v>
+        <v>-2.1451</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5051</v>
+        <v>-0.8946</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0902</v>
+        <v>-1.2505</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9163</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8326</v>
+        <v>-2.7489</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9163</v>
+        <v>0.733</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0574</v>
+        <v>-1.5253</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6018</v>
+        <v>-0.8495</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6592</v>
+        <v>-0.6757</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5681</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.0208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. CARRION BALLESTER</t>
+          <t>H. MARI LOPEZ-ROCA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.4429</v>
+        <v>-6.5224</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6523</v>
+        <v>-4.6949</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7905</v>
+        <v>-1.8275</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.8005</v>
+        <v>-4.0162</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3099</v>
+        <v>-2.6152</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4905</v>
+        <v>-1.401</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6554</v>
+        <v>-1.8164</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4154</v>
+        <v>-1.217</v>
       </c>
       <c r="L10" t="n">
-        <v>0.76</v>
+        <v>-0.5994</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1451</v>
+        <v>-2.1999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8946</v>
+        <v>-1.3982</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2505</v>
+        <v>-0.8017</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0158</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R10" t="n">
-        <v>0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6265</v>
+        <v>-1.5899</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2481</v>
+        <v>-1.046</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3785</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. MARI LOPEZ-ROCA</t>
+          <t>C. HORTELANO ESCRIBA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.6023</v>
+        <v>-7.0029</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.75</v>
+        <v>-4.6686</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8523</v>
+        <v>-2.3343</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.0162</v>
+        <v>-6.6606</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.6152</v>
+        <v>-3.7723</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.401</v>
+        <v>-2.8883</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.8164</v>
+        <v>-4.0653</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.217</v>
+        <v>-2.2672</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5994</v>
+        <v>-1.7981</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1999</v>
+        <v>-2.5953</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3982</v>
+        <v>-1.5051</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8017</v>
+        <v>-1.0902</v>
       </c>
       <c r="P11" t="n">
         <v>-0.9163</v>
@@ -1312,22 +1312,22 @@
         <v>0.9163</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6697</v>
+        <v>-0.9942</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.101</v>
+        <v>-0.3597</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5687</v>
+        <v>-0.6345</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.5681</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.0208</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-30.1637</v>
+        <v>-29.6132</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.8189</v>
+        <v>-11.2682</v>
       </c>
       <c r="F12" t="n">
         <v>-18.3448</v>
@@ -1363,7 +1363,7 @@
         <v>-1.9245</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6456000000000004</v>
+        <v>-0.6456</v>
       </c>
       <c r="K12" t="n">
         <v>-2.0898</v>
@@ -1390,16 +1390,16 @@
         <v>8.246599999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-12.9185</v>
+        <v>-12.3681</v>
       </c>
       <c r="T12" t="n">
-        <v>-7.4394</v>
+        <v>-6.889</v>
       </c>
       <c r="U12" t="n">
         <v>-5.479</v>
       </c>
       <c r="V12" t="n">
-        <v>3.7593</v>
+        <v>3.759300000000001</v>
       </c>
       <c r="W12" t="n">
         <v>6.345199999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. IGBINS DAVID</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.4239</v>
+        <v>6.1058</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6519</v>
+        <v>4.9245</v>
       </c>
       <c r="F13" t="n">
-        <v>2.772</v>
+        <v>1.1813</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6649</v>
+        <v>4.2425</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7835</v>
+        <v>4.1846</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1187</v>
+        <v>0.0579</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2712</v>
+        <v>4.4871</v>
       </c>
       <c r="K13" t="n">
-        <v>3.0371</v>
+        <v>3.6597</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2341</v>
+        <v>0.8274</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6063</v>
+        <v>-0.2446</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2535</v>
+        <v>0.5249</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3528</v>
+        <v>-0.7695</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8326</v>
+        <v>0.733</v>
       </c>
       <c r="S13" t="n">
-        <v>5.7486</v>
+        <v>2.3686</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5694</v>
+        <v>1.3537</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1792</v>
+        <v>1.0149</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0104</v>
+        <v>-0.3219</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6335</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>D. GARCIA ROYO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.5322</v>
+        <v>5.79</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0784</v>
+        <v>2.5682</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4538</v>
+        <v>3.2218</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2425</v>
+        <v>4.5698</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1846</v>
+        <v>4.7397</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0579</v>
+        <v>-0.1699</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4871</v>
+        <v>3.3704</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6597</v>
+        <v>3.8607</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8274</v>
+        <v>-0.4902</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2446</v>
+        <v>1.1994</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5249</v>
+        <v>0.879</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7695</v>
+        <v>0.3204</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R14" t="n">
-        <v>0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="S14" t="n">
-        <v>3.7949</v>
+        <v>1.5213</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5076</v>
+        <v>0.4152</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2874</v>
+        <v>1.1061</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3219</v>
+        <v>-0.3011</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. GARCIA ROYO</t>
+          <t>A. IGBINS DAVID</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.6015</v>
+        <v>5.5842</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4336</v>
+        <v>3.7288</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1679</v>
+        <v>1.8553</v>
       </c>
       <c r="G15" t="n">
-        <v>4.5698</v>
+        <v>2.6649</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7397</v>
+        <v>2.7835</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1699</v>
+        <v>-0.1187</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3704</v>
+        <v>3.2712</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8607</v>
+        <v>3.0371</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.4902</v>
+        <v>0.2341</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1994</v>
+        <v>-0.6063</v>
       </c>
       <c r="N15" t="n">
-        <v>0.879</v>
+        <v>-0.2535</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3204</v>
+        <v>-0.3528</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9163</v>
+        <v>1.8326</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3328</v>
+        <v>2.9089</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2806</v>
+        <v>1.6463</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0522</v>
+        <v>1.2626</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3011</v>
+        <v>0.0104</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3011</v>
+        <v>0.6439</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8077</v>
+        <v>4.3788</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6847</v>
+        <v>2.7808</v>
       </c>
       <c r="F16" t="n">
-        <v>1.123</v>
+        <v>1.598</v>
       </c>
       <c r="G16" t="n">
         <v>1.588</v>
@@ -1702,13 +1702,13 @@
         <v>1.0995</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4213</v>
+        <v>1.9925</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9503</v>
+        <v>1.0464</v>
       </c>
       <c r="U16" t="n">
-        <v>0.471</v>
+        <v>0.946</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3011</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6141</v>
+        <v>4.3658</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7349</v>
+        <v>1.408</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8792</v>
+        <v>2.9578</v>
       </c>
       <c r="G17" t="n">
         <v>4.157</v>
@@ -1780,13 +1780,13 @@
         <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3342</v>
+        <v>1.086</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8627</v>
+        <v>-0.1896</v>
       </c>
       <c r="U17" t="n">
-        <v>1.197</v>
+        <v>1.2756</v>
       </c>
       <c r="V17" t="n">
         <v>0.9554</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALÁN</t>
+          <t>J. VILLAR SOLER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.1507</v>
+        <v>3.8189</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1507</v>
+        <v>2.1698</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.6491</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1507</v>
+        <v>2.6236</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6502</v>
+        <v>0.5558</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5005</v>
+        <v>2.0678</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1507</v>
+        <v>2.7079</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6502</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5005</v>
+        <v>2.036</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-0.0843</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.1161</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.0318</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.3786</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.3782</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.0004</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. NOS BARBERA</t>
+          <t>A. CEJUDO GALÁN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6359</v>
+        <v>3.1507</v>
       </c>
       <c r="E19" t="n">
-        <v>1.796</v>
+        <v>3.1507</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8399</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1.03</v>
+        <v>3.1507</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2509</v>
+        <v>0.6502</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7791</v>
+        <v>2.5005</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6942</v>
+        <v>3.1507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0433</v>
+        <v>0.6502</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6509</v>
+        <v>2.5005</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3357</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2075</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1282</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2108</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1652</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0456</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. VILLAR SOLER</t>
+          <t>M. NOS BARBERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1871</v>
+        <v>2.856</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1121</v>
+        <v>1.8922</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0749</v>
+        <v>0.9638</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6236</v>
+        <v>1.03</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5558</v>
+        <v>0.2509</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0678</v>
+        <v>0.7791</v>
       </c>
       <c r="J20" t="n">
-        <v>2.7079</v>
+        <v>0.6942</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="L20" t="n">
-        <v>2.036</v>
+        <v>0.6509</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0843</v>
+        <v>0.3357</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1161</v>
+        <v>0.2075</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0318</v>
+        <v>0.1282</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1833</v>
+        <v>0.5498</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2532</v>
+        <v>0.0092</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6795</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4262</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. PEREZ RIPOLL</t>
+          <t>A. CEJUDO GALAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.596</v>
+        <v>-0.1293</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1701</v>
+        <v>-0.0382</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5741000000000001</v>
+        <v>-0.0911</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1891</v>
+        <v>-1.2443</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.327</v>
+        <v>-0.9717</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8621</v>
+        <v>-0.2726</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4438</v>
+        <v>-0.6868</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2292</v>
+        <v>-0.8952</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2146</v>
+        <v>0.2084</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2548</v>
+        <v>-0.5575</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0977</v>
+        <v>-0.0765</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3525</v>
+        <v>-0.481</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9438</v>
+        <v>1.0992</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2738</v>
+        <v>0.6486</v>
       </c>
       <c r="U21" t="n">
-        <v>0.67</v>
+        <v>0.4506</v>
       </c>
       <c r="V21" t="n">
         <v>-1.267</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALAN</t>
+          <t>A. PEREZ RIPOLL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7232</v>
+        <v>-0.9121</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3844</v>
+        <v>-1.3624</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3388</v>
+        <v>0.4502</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2443</v>
+        <v>-1.1891</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9717</v>
+        <v>-0.327</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2726</v>
+        <v>-0.8621</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6868</v>
+        <v>-1.4438</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8952</v>
+        <v>-0.2292</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2084</v>
+        <v>-1.2146</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5575</v>
+        <v>0.2548</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0765</v>
+        <v>-0.0977</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.481</v>
+        <v>0.3525</v>
       </c>
       <c r="P22" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4947</v>
+        <v>0.6276</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6976</v>
+        <v>0.0815</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2029</v>
+        <v>0.5462</v>
       </c>
       <c r="V22" t="n">
         <v>-1.267</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.47</v>
+        <v>-4.2039</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7429</v>
+        <v>-2.8775</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7271</v>
+        <v>-1.3264</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4209</v>
@@ -2248,13 +2248,13 @@
         <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6984</v>
+        <v>0.5677</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6976</v>
+        <v>0.1678</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0008</v>
+        <v>0.3999</v>
       </c>
       <c r="V23" t="n">
         <v>-2.5339</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>30.16390000000001</v>
+        <v>30.8049</v>
       </c>
       <c r="E24" t="n">
         <v>18.3449</v>
       </c>
       <c r="F24" t="n">
-        <v>11.8189</v>
+        <v>12.4598</v>
       </c>
       <c r="G24" t="n">
         <v>19.1722</v>
@@ -2326,13 +2326,13 @@
         <v>10.0791</v>
       </c>
       <c r="S24" t="n">
-        <v>12.9185</v>
+        <v>13.5596</v>
       </c>
       <c r="T24" t="n">
         <v>5.479100000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>7.4395</v>
+        <v>8.080499999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-3.7592</v>
